--- a/perception_pipeline_benchmarking.xlsx
+++ b/perception_pipeline_benchmarking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bilou\Documents\PHD\ROS_WS\src\pcl_package\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F70D13DB-4079-4730-A3C4-EB14801A6C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB437837-5014-4E11-BFE5-C470D38F2D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C70BF8C6-7E3B-42DE-8AC7-C41728DABEC7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>CYLINDER</t>
   </si>
@@ -60,6 +60,33 @@
   </si>
   <si>
     <t>5 : ~vue 1, dans le noir</t>
+  </si>
+  <si>
+    <t>SPHERE</t>
+  </si>
+  <si>
+    <t>vue 2, éloigné</t>
+  </si>
+  <si>
+    <t>vue 1, lumière off</t>
+  </si>
+  <si>
+    <t>vue 2, lumière off</t>
+  </si>
+  <si>
+    <t>PLATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vue 1, proche </t>
+  </si>
+  <si>
+    <t xml:space="preserve">vue 1, éloigné </t>
+  </si>
+  <si>
+    <t>vue 2, proche</t>
+  </si>
+  <si>
+    <t>vue 1, proche</t>
   </si>
 </sst>
 </file>
@@ -431,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7839B3DB-F1A7-44B4-A862-78A4FB234A45}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.44140625" customWidth="1"/>
@@ -649,6 +676,386 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>0.04</v>
+      </c>
+      <c r="C14">
+        <v>0.04</v>
+      </c>
+      <c r="D14">
+        <v>0.04</v>
+      </c>
+      <c r="E14">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="F14">
+        <v>4.7E-2</v>
+      </c>
+      <c r="G14">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>0.05</v>
+      </c>
+      <c r="C15">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="D15">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="E15">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="F15">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>0.06</v>
+      </c>
+      <c r="C16">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="D16">
+        <v>0.05</v>
+      </c>
+      <c r="E16">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="F16">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="G16">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="C17">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="D17">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="E17">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="F17">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="G17">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C18">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="D18">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="E18">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="F18">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="G18">
+        <v>7.0999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="C19">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="D19">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E19">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="F19">
+        <v>0.08</v>
+      </c>
+      <c r="G19">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>0.08</v>
+      </c>
+      <c r="C20">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D20">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="E20">
+        <v>0.09</v>
+      </c>
+      <c r="F20">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="G20">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="C21">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="D21">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="E21">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="F21">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="G21">
+        <v>8.4000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>0.09</v>
+      </c>
+      <c r="C22">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="D22">
+        <v>0.08</v>
+      </c>
+      <c r="E22">
+        <v>0.08</v>
+      </c>
+      <c r="F22">
+        <v>0.09</v>
+      </c>
+      <c r="G22">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>0.01</v>
+      </c>
+      <c r="C25">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D25">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E25">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="F25">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G25">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="C26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D26">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F26">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="G26">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>0.02</v>
+      </c>
+      <c r="C27">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D27">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="E27">
+        <v>0.02</v>
+      </c>
+      <c r="F27">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G27">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C28">
+        <v>2.4E-2</v>
+      </c>
+      <c r="D28">
+        <v>3.1E-2</v>
+      </c>
+      <c r="E28">
+        <v>2.4E-2</v>
+      </c>
+      <c r="F28">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G28">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>0.03</v>
+      </c>
+      <c r="C29">
+        <v>0.03</v>
+      </c>
+      <c r="D29">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E29">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F29">
+        <v>3.1E-2</v>
+      </c>
+      <c r="G29">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="C30">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D30">
+        <v>0.04</v>
+      </c>
+      <c r="E30">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F30">
+        <v>4.7E-2</v>
+      </c>
+      <c r="G30">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>0.04</v>
+      </c>
+      <c r="C31">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D31">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="E31">
+        <v>3.9E-2</v>
+      </c>
+      <c r="F31">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G31">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C32">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D32">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="E32">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="F32">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G32">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
